--- a/0_Resources/Excel Shortcuts.xlsx
+++ b/0_Resources/Excel Shortcuts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Mac\Home\Developer\_Courses\Excel\Excel_Data_Analytics_Course\0_Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marketing/Desktop/TGC_Code_Base/Excel_Data_Analytics_Course/0_Resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E66C5D-F031-43A0-B584-883D613AEA9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11EDBB75-7092-BF4C-BA9C-69B7C6C5F09C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-78" yWindow="384" windowWidth="18336" windowHeight="11592" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="18340" windowHeight="11600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>Group</t>
   </si>
@@ -185,6 +185,9 @@
   </si>
   <si>
     <t>Increase height of formula bar</t>
+  </si>
+  <si>
+    <t>a</t>
   </si>
 </sst>
 </file>
@@ -222,7 +225,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -365,11 +368,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -386,6 +400,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -690,15 +705,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -709,7 +724,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
@@ -720,7 +735,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="5"/>
       <c r="B3" s="1" t="s">
         <v>10</v>
@@ -729,7 +744,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
       <c r="B4" s="1" t="s">
         <v>11</v>
@@ -738,7 +753,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
@@ -749,7 +764,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
       <c r="B6" s="1" t="s">
         <v>13</v>
@@ -758,7 +773,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
@@ -769,7 +784,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="5"/>
       <c r="B8" s="1" t="s">
         <v>15</v>
@@ -778,7 +793,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="5"/>
       <c r="B9" s="1" t="s">
         <v>16</v>
@@ -787,7 +802,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>6</v>
       </c>
@@ -798,7 +813,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="5"/>
       <c r="B11" s="1" t="s">
         <v>18</v>
@@ -807,7 +822,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="5"/>
       <c r="B12" s="1" t="s">
         <v>19</v>
@@ -816,7 +831,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
       <c r="B13" s="1" t="s">
         <v>20</v>
@@ -825,7 +840,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>7</v>
       </c>
@@ -836,7 +851,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="5"/>
       <c r="B15" s="1" t="s">
         <v>22</v>
@@ -845,7 +860,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="5"/>
       <c r="B16" s="1" t="s">
         <v>23</v>
@@ -854,7 +869,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>8</v>
       </c>
@@ -865,7 +880,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="1" t="s">
         <v>25</v>
@@ -874,7 +889,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" s="1" t="s">
         <v>26</v>
@@ -883,7 +898,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="1" t="s">
         <v>27</v>
@@ -892,7 +907,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="5"/>
       <c r="B21" s="1" t="s">
         <v>28</v>
@@ -901,7 +916,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="5"/>
       <c r="B22" s="1" t="s">
         <v>29</v>
@@ -910,7 +925,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5"/>
       <c r="B23" s="1" t="s">
         <v>30</v>
@@ -919,13 +934,18 @@
         <v>53</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7"/>
       <c r="B24" s="8" t="s">
         <v>31</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C25" s="10" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
